--- a/static/school.xlsx
+++ b/static/school.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AFTOOL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zfp69\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EAC2F6-431D-4F89-B8CB-5F5174E5BE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD58337C-FEB0-4917-9381-7CF15F15D514}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4690" yWindow="2750" windowWidth="25600" windowHeight="11710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="1052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="1053">
   <si>
     <t>1-1</t>
   </si>
@@ -3199,6 +3188,9 @@
   </si>
   <si>
     <t>3970985006</t>
+  </si>
+  <si>
+    <t>397094600Y</t>
   </si>
 </sst>
 </file>
@@ -3533,13 +3525,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C351"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1049</v>
       </c>
@@ -3550,7 +3542,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>364</v>
       </c>
@@ -3561,7 +3553,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>366</v>
       </c>
@@ -3572,7 +3564,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>368</v>
       </c>
@@ -3583,7 +3575,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>370</v>
       </c>
@@ -3594,7 +3586,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>372</v>
       </c>
@@ -3605,7 +3597,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>374</v>
       </c>
@@ -3616,7 +3608,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>376</v>
       </c>
@@ -3627,7 +3619,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>378</v>
       </c>
@@ -3638,7 +3630,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>380</v>
       </c>
@@ -3649,7 +3641,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>382</v>
       </c>
@@ -3660,7 +3652,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>384</v>
       </c>
@@ -3671,7 +3663,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>386</v>
       </c>
@@ -3682,7 +3674,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>388</v>
       </c>
@@ -3693,7 +3685,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>390</v>
       </c>
@@ -3704,7 +3696,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>392</v>
       </c>
@@ -3715,7 +3707,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>394</v>
       </c>
@@ -3726,7 +3718,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>396</v>
       </c>
@@ -3737,7 +3729,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>398</v>
       </c>
@@ -3748,7 +3740,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>400</v>
       </c>
@@ -3759,7 +3751,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>402</v>
       </c>
@@ -3770,7 +3762,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>404</v>
       </c>
@@ -3781,7 +3773,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>406</v>
       </c>
@@ -3792,7 +3784,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>408</v>
       </c>
@@ -3803,7 +3795,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>410</v>
       </c>
@@ -3814,7 +3806,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>412</v>
       </c>
@@ -3825,7 +3817,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>414</v>
       </c>
@@ -3836,7 +3828,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>416</v>
       </c>
@@ -3847,7 +3839,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>418</v>
       </c>
@@ -3858,7 +3850,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>420</v>
       </c>
@@ -3869,7 +3861,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>422</v>
       </c>
@@ -3880,7 +3872,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>354</v>
       </c>
@@ -3891,7 +3883,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>353</v>
       </c>
@@ -3902,7 +3894,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>424</v>
       </c>
@@ -3913,7 +3905,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>426</v>
       </c>
@@ -3924,7 +3916,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>428</v>
       </c>
@@ -3935,7 +3927,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>430</v>
       </c>
@@ -3946,7 +3938,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>432</v>
       </c>
@@ -3957,7 +3949,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>434</v>
       </c>
@@ -3968,7 +3960,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>436</v>
       </c>
@@ -3979,7 +3971,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>438</v>
       </c>
@@ -3990,7 +3982,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>440</v>
       </c>
@@ -4001,7 +3993,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>356</v>
       </c>
@@ -4012,7 +4004,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>442</v>
       </c>
@@ -4023,7 +4015,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>444</v>
       </c>
@@ -4034,7 +4026,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>446</v>
       </c>
@@ -4045,7 +4037,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>448</v>
       </c>
@@ -4056,7 +4048,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>450</v>
       </c>
@@ -4067,7 +4059,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>452</v>
       </c>
@@ -4078,7 +4070,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>454</v>
       </c>
@@ -4089,7 +4081,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>456</v>
       </c>
@@ -4100,7 +4092,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>458</v>
       </c>
@@ -4111,7 +4103,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>460</v>
       </c>
@@ -4122,7 +4114,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>462</v>
       </c>
@@ -4133,7 +4125,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>464</v>
       </c>
@@ -4144,7 +4136,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>466</v>
       </c>
@@ -4155,7 +4147,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>468</v>
       </c>
@@ -4166,7 +4158,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>470</v>
       </c>
@@ -4177,7 +4169,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>472</v>
       </c>
@@ -4188,7 +4180,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>474</v>
       </c>
@@ -4199,7 +4191,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>476</v>
       </c>
@@ -4210,7 +4202,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>478</v>
       </c>
@@ -4221,7 +4213,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>480</v>
       </c>
@@ -4232,7 +4224,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>482</v>
       </c>
@@ -4243,7 +4235,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>484</v>
       </c>
@@ -4254,7 +4246,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>486</v>
       </c>
@@ -4265,7 +4257,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>488</v>
       </c>
@@ -4276,7 +4268,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>490</v>
       </c>
@@ -4287,7 +4279,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>492</v>
       </c>
@@ -4298,7 +4290,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>494</v>
       </c>
@@ -4309,7 +4301,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>496</v>
       </c>
@@ -4320,7 +4312,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>498</v>
       </c>
@@ -4331,7 +4323,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>500</v>
       </c>
@@ -4342,7 +4334,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>502</v>
       </c>
@@ -4353,7 +4345,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>504</v>
       </c>
@@ -4364,7 +4356,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>506</v>
       </c>
@@ -4375,7 +4367,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>508</v>
       </c>
@@ -4386,7 +4378,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>510</v>
       </c>
@@ -4397,7 +4389,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>512</v>
       </c>
@@ -4408,7 +4400,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>514</v>
       </c>
@@ -4419,7 +4411,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>516</v>
       </c>
@@ -4430,7 +4422,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>518</v>
       </c>
@@ -4441,7 +4433,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>520</v>
       </c>
@@ -4452,7 +4444,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>522</v>
       </c>
@@ -4463,7 +4455,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>524</v>
       </c>
@@ -4474,7 +4466,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>526</v>
       </c>
@@ -4485,7 +4477,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>1051</v>
       </c>
@@ -4496,7 +4488,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>528</v>
       </c>
@@ -4507,7 +4499,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>530</v>
       </c>
@@ -4518,7 +4510,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>532</v>
       </c>
@@ -4529,7 +4521,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>534</v>
       </c>
@@ -4540,7 +4532,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>536</v>
       </c>
@@ -4551,7 +4543,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>538</v>
       </c>
@@ -4562,7 +4554,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>540</v>
       </c>
@@ -4573,7 +4565,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>542</v>
       </c>
@@ -4584,7 +4576,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>544</v>
       </c>
@@ -4595,7 +4587,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>546</v>
       </c>
@@ -4606,7 +4598,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>548</v>
       </c>
@@ -4617,7 +4609,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>550</v>
       </c>
@@ -4628,7 +4620,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>552</v>
       </c>
@@ -4639,7 +4631,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>554</v>
       </c>
@@ -4650,7 +4642,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>556</v>
       </c>
@@ -4661,7 +4653,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>558</v>
       </c>
@@ -4672,7 +4664,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>560</v>
       </c>
@@ -4683,7 +4675,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>562</v>
       </c>
@@ -4694,7 +4686,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>564</v>
       </c>
@@ -4705,7 +4697,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>566</v>
       </c>
@@ -4716,7 +4708,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>568</v>
       </c>
@@ -4727,7 +4719,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>570</v>
       </c>
@@ -4738,7 +4730,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>572</v>
       </c>
@@ -4749,7 +4741,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>574</v>
       </c>
@@ -4760,7 +4752,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>576</v>
       </c>
@@ -4771,7 +4763,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>578</v>
       </c>
@@ -4782,7 +4774,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>580</v>
       </c>
@@ -4793,7 +4785,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>582</v>
       </c>
@@ -4804,7 +4796,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>584</v>
       </c>
@@ -4815,7 +4807,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>586</v>
       </c>
@@ -4826,7 +4818,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>588</v>
       </c>
@@ -4837,7 +4829,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>590</v>
       </c>
@@ -4848,7 +4840,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>592</v>
       </c>
@@ -4859,7 +4851,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>594</v>
       </c>
@@ -4870,7 +4862,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>596</v>
       </c>
@@ -4881,7 +4873,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>598</v>
       </c>
@@ -4892,7 +4884,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>600</v>
       </c>
@@ -4903,7 +4895,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>602</v>
       </c>
@@ -4914,7 +4906,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>604</v>
       </c>
@@ -4925,7 +4917,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>606</v>
       </c>
@@ -4936,7 +4928,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>608</v>
       </c>
@@ -4947,7 +4939,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>610</v>
       </c>
@@ -4958,7 +4950,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>612</v>
       </c>
@@ -4969,7 +4961,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>614</v>
       </c>
@@ -4980,7 +4972,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>615</v>
       </c>
@@ -4991,7 +4983,10 @@
         <v>357</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>1052</v>
+      </c>
       <c r="B133" t="s">
         <v>131</v>
       </c>
@@ -4999,7 +4994,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>617</v>
       </c>
@@ -5010,7 +5005,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>619</v>
       </c>
@@ -5021,7 +5016,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>621</v>
       </c>
@@ -5032,7 +5027,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>623</v>
       </c>
@@ -5043,7 +5038,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>625</v>
       </c>
@@ -5054,7 +5049,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>627</v>
       </c>
@@ -5065,7 +5060,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>629</v>
       </c>
@@ -5076,7 +5071,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>631</v>
       </c>
@@ -5087,7 +5082,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>633</v>
       </c>
@@ -5098,7 +5093,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>635</v>
       </c>
@@ -5109,7 +5104,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>637</v>
       </c>
@@ -5120,7 +5115,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>639</v>
       </c>
@@ -5131,7 +5126,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>641</v>
       </c>
@@ -5142,7 +5137,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>643</v>
       </c>
@@ -5153,7 +5148,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>645</v>
       </c>
@@ -5164,7 +5159,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>647</v>
       </c>
@@ -5175,7 +5170,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>649</v>
       </c>
@@ -5186,7 +5181,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>651</v>
       </c>
@@ -5197,7 +5192,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>653</v>
       </c>
@@ -5208,7 +5203,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>655</v>
       </c>
@@ -5219,7 +5214,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>657</v>
       </c>
@@ -5230,7 +5225,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>659</v>
       </c>
@@ -5241,7 +5236,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>661</v>
       </c>
@@ -5252,7 +5247,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>663</v>
       </c>
@@ -5263,7 +5258,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>665</v>
       </c>
@@ -5274,7 +5269,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>667</v>
       </c>
@@ -5285,7 +5280,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>669</v>
       </c>
@@ -5296,7 +5291,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>671</v>
       </c>
@@ -5307,7 +5302,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>673</v>
       </c>
@@ -5318,7 +5313,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>675</v>
       </c>
@@ -5329,7 +5324,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>677</v>
       </c>
@@ -5340,7 +5335,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>679</v>
       </c>
@@ -5351,7 +5346,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>681</v>
       </c>
@@ -5362,7 +5357,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>683</v>
       </c>
@@ -5373,7 +5368,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>685</v>
       </c>
@@ -5384,7 +5379,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>687</v>
       </c>
@@ -5395,7 +5390,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>689</v>
       </c>
@@ -5406,7 +5401,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>691</v>
       </c>
@@ -5417,7 +5412,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>693</v>
       </c>
@@ -5428,7 +5423,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>695</v>
       </c>
@@ -5439,7 +5434,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>697</v>
       </c>
@@ -5450,7 +5445,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>699</v>
       </c>
@@ -5461,7 +5456,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>701</v>
       </c>
@@ -5472,7 +5467,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>703</v>
       </c>
@@ -5483,7 +5478,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>705</v>
       </c>
@@ -5494,7 +5489,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>707</v>
       </c>
@@ -5505,7 +5500,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>709</v>
       </c>
@@ -5516,7 +5511,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>711</v>
       </c>
@@ -5527,7 +5522,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>713</v>
       </c>
@@ -5538,7 +5533,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>715</v>
       </c>
@@ -5549,7 +5544,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>717</v>
       </c>
@@ -5560,7 +5555,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>719</v>
       </c>
@@ -5571,7 +5566,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>721</v>
       </c>
@@ -5582,7 +5577,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>723</v>
       </c>
@@ -5593,7 +5588,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>725</v>
       </c>
@@ -5604,7 +5599,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>727</v>
       </c>
@@ -5615,7 +5610,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>360</v>
       </c>
@@ -5626,7 +5621,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>729</v>
       </c>
@@ -5637,7 +5632,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>731</v>
       </c>
@@ -5648,7 +5643,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>733</v>
       </c>
@@ -5659,7 +5654,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>735</v>
       </c>
@@ -5670,7 +5665,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>737</v>
       </c>
@@ -5681,7 +5676,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>739</v>
       </c>
@@ -5692,7 +5687,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>741</v>
       </c>
@@ -5703,7 +5698,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>743</v>
       </c>
@@ -5714,7 +5709,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>745</v>
       </c>
@@ -5725,7 +5720,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>747</v>
       </c>
@@ -5736,7 +5731,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>749</v>
       </c>
@@ -5747,7 +5742,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>751</v>
       </c>
@@ -5758,7 +5753,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>753</v>
       </c>
@@ -5769,7 +5764,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>755</v>
       </c>
@@ -5780,7 +5775,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>757</v>
       </c>
@@ -5791,7 +5786,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>759</v>
       </c>
@@ -5802,7 +5797,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>761</v>
       </c>
@@ -5813,7 +5808,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>763</v>
       </c>
@@ -5824,7 +5819,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>765</v>
       </c>
@@ -5835,7 +5830,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>767</v>
       </c>
@@ -5846,7 +5841,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>769</v>
       </c>
@@ -5857,7 +5852,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>771</v>
       </c>
@@ -5868,7 +5863,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>773</v>
       </c>
@@ -5879,7 +5874,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>775</v>
       </c>
@@ -5890,7 +5885,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>777</v>
       </c>
@@ -5901,7 +5896,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>779</v>
       </c>
@@ -5912,7 +5907,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>781</v>
       </c>
@@ -5923,7 +5918,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>783</v>
       </c>
@@ -5934,7 +5929,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>785</v>
       </c>
@@ -5945,7 +5940,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>787</v>
       </c>
@@ -5956,7 +5951,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>789</v>
       </c>
@@ -5967,7 +5962,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>791</v>
       </c>
@@ -5978,7 +5973,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>793</v>
       </c>
@@ -5989,7 +5984,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>795</v>
       </c>
@@ -6000,7 +5995,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>797</v>
       </c>
@@ -6011,7 +6006,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>799</v>
       </c>
@@ -6022,7 +6017,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>801</v>
       </c>
@@ -6033,7 +6028,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>803</v>
       </c>
@@ -6044,7 +6039,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>805</v>
       </c>
@@ -6055,7 +6050,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>807</v>
       </c>
@@ -6066,7 +6061,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>809</v>
       </c>
@@ -6077,7 +6072,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>811</v>
       </c>
@@ -6088,7 +6083,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>813</v>
       </c>
@@ -6099,7 +6094,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>815</v>
       </c>
@@ -6110,7 +6105,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>817</v>
       </c>
@@ -6121,7 +6116,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>819</v>
       </c>
@@ -6132,7 +6127,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>821</v>
       </c>
@@ -6143,7 +6138,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>823</v>
       </c>
@@ -6154,7 +6149,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>825</v>
       </c>
@@ -6165,7 +6160,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>827</v>
       </c>
@@ -6176,7 +6171,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>829</v>
       </c>
@@ -6187,7 +6182,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>831</v>
       </c>
@@ -6198,7 +6193,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>833</v>
       </c>
@@ -6209,7 +6204,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>835</v>
       </c>
@@ -6220,7 +6215,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>837</v>
       </c>
@@ -6231,7 +6226,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>839</v>
       </c>
@@ -6242,7 +6237,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>841</v>
       </c>
@@ -6253,7 +6248,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>843</v>
       </c>
@@ -6264,7 +6259,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>845</v>
       </c>
@@ -6275,7 +6270,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>847</v>
       </c>
@@ -6286,7 +6281,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>849</v>
       </c>
@@ -6297,7 +6292,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>851</v>
       </c>
@@ -6308,7 +6303,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>853</v>
       </c>
@@ -6319,7 +6314,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>855</v>
       </c>
@@ -6330,7 +6325,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>857</v>
       </c>
@@ -6341,7 +6336,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>859</v>
       </c>
@@ -6352,7 +6347,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>861</v>
       </c>
@@ -6363,7 +6358,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>863</v>
       </c>
@@ -6374,7 +6369,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>865</v>
       </c>
@@ -6385,7 +6380,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>867</v>
       </c>
@@ -6396,7 +6391,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>869</v>
       </c>
@@ -6407,7 +6402,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>871</v>
       </c>
@@ -6418,7 +6413,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>873</v>
       </c>
@@ -6429,7 +6424,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>875</v>
       </c>
@@ -6440,7 +6435,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>877</v>
       </c>
@@ -6451,7 +6446,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>879</v>
       </c>
@@ -6462,7 +6457,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>881</v>
       </c>
@@ -6473,7 +6468,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>883</v>
       </c>
@@ -6484,7 +6479,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>885</v>
       </c>
@@ -6495,7 +6490,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>887</v>
       </c>
@@ -6506,7 +6501,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>889</v>
       </c>
@@ -6517,7 +6512,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>891</v>
       </c>
@@ -6528,7 +6523,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>893</v>
       </c>
@@ -6539,7 +6534,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>895</v>
       </c>
@@ -6550,7 +6545,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>897</v>
       </c>
@@ -6561,7 +6556,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>899</v>
       </c>
@@ -6572,7 +6567,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>901</v>
       </c>
@@ -6583,7 +6578,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>903</v>
       </c>
@@ -6594,7 +6589,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>905</v>
       </c>
@@ -6605,7 +6600,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>907</v>
       </c>
@@ -6616,7 +6611,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>909</v>
       </c>
@@ -6627,7 +6622,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>911</v>
       </c>
@@ -6638,7 +6633,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>913</v>
       </c>
@@ -6649,7 +6644,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>915</v>
       </c>
@@ -6660,7 +6655,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>917</v>
       </c>
@@ -6671,7 +6666,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>362</v>
       </c>
@@ -6682,7 +6677,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>919</v>
       </c>
@@ -6693,7 +6688,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>921</v>
       </c>
@@ -6704,7 +6699,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>923</v>
       </c>
@@ -6715,7 +6710,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>925</v>
       </c>
@@ -6726,7 +6721,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>927</v>
       </c>
@@ -6737,7 +6732,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>929</v>
       </c>
@@ -6748,7 +6743,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>931</v>
       </c>
@@ -6759,7 +6754,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>933</v>
       </c>
@@ -6770,7 +6765,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>935</v>
       </c>
@@ -6781,7 +6776,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>937</v>
       </c>
@@ -6792,7 +6787,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>939</v>
       </c>
@@ -6803,7 +6798,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>941</v>
       </c>
@@ -6814,7 +6809,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>943</v>
       </c>
@@ -6825,7 +6820,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>945</v>
       </c>
@@ -6836,7 +6831,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>947</v>
       </c>
@@ -6847,7 +6842,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>949</v>
       </c>
@@ -6858,7 +6853,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>951</v>
       </c>
@@ -6869,7 +6864,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>953</v>
       </c>
@@ -6880,7 +6875,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>955</v>
       </c>
@@ -6891,7 +6886,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>957</v>
       </c>
@@ -6902,7 +6897,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>959</v>
       </c>
@@ -6913,7 +6908,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>961</v>
       </c>
@@ -6924,7 +6919,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>963</v>
       </c>
@@ -6935,7 +6930,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>965</v>
       </c>
@@ -6946,7 +6941,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>967</v>
       </c>
@@ -6957,7 +6952,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>969</v>
       </c>
@@ -6968,7 +6963,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>971</v>
       </c>
@@ -6979,7 +6974,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>973</v>
       </c>
@@ -6990,7 +6985,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>975</v>
       </c>
@@ -7001,7 +6996,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>977</v>
       </c>
@@ -7012,7 +7007,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>979</v>
       </c>
@@ -7023,7 +7018,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>981</v>
       </c>
@@ -7034,7 +7029,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>983</v>
       </c>
@@ -7045,7 +7040,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>985</v>
       </c>
@@ -7056,7 +7051,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>987</v>
       </c>
@@ -7067,7 +7062,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>989</v>
       </c>
@@ -7078,7 +7073,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>991</v>
       </c>
@@ -7089,7 +7084,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>993</v>
       </c>
@@ -7100,7 +7095,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>995</v>
       </c>
@@ -7111,7 +7106,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>997</v>
       </c>
@@ -7122,7 +7117,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>999</v>
       </c>
@@ -7133,7 +7128,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>1001</v>
       </c>
@@ -7144,7 +7139,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>1003</v>
       </c>
@@ -7155,7 +7150,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>1005</v>
       </c>
@@ -7166,7 +7161,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>1007</v>
       </c>
@@ -7177,7 +7172,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>1009</v>
       </c>
@@ -7188,7 +7183,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>1011</v>
       </c>
@@ -7199,7 +7194,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>1013</v>
       </c>
@@ -7210,7 +7205,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>1015</v>
       </c>
@@ -7221,7 +7216,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>1017</v>
       </c>
@@ -7232,7 +7227,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>1019</v>
       </c>
@@ -7243,7 +7238,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>1021</v>
       </c>
@@ -7254,7 +7249,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>1023</v>
       </c>
@@ -7265,7 +7260,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>1025</v>
       </c>
@@ -7276,7 +7271,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>1027</v>
       </c>
@@ -7287,7 +7282,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>1029</v>
       </c>
@@ -7298,7 +7293,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>1031</v>
       </c>
@@ -7309,7 +7304,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>1033</v>
       </c>
@@ -7320,7 +7315,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>1035</v>
       </c>
@@ -7331,7 +7326,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>1037</v>
       </c>
@@ -7342,7 +7337,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>1039</v>
       </c>
@@ -7353,7 +7348,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>1041</v>
       </c>
@@ -7364,7 +7359,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>1043</v>
       </c>
@@ -7375,7 +7370,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>1045</v>
       </c>
@@ -7386,7 +7381,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>1047</v>
       </c>
